--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>80.35752666112519</v>
+        <v>13.05809808243284</v>
       </c>
       <c r="D2" t="n">
-        <v>31.86637924945785</v>
+        <v>5.178286628036901</v>
       </c>
       <c r="E2" t="n">
-        <v>16.84883050814847</v>
+        <v>2.737934957574126</v>
       </c>
       <c r="F2" t="n">
-        <v>4.001407605260112</v>
+        <v>0.6502287358547683</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.78451974481401</v>
+        <v>8.252484458532276</v>
       </c>
       <c r="D3" t="n">
-        <v>40.04511502152825</v>
+        <v>6.507331190998341</v>
       </c>
       <c r="E3" t="n">
-        <v>16.84883050814847</v>
+        <v>2.737934957574126</v>
       </c>
       <c r="F3" t="n">
-        <v>4.001407605260112</v>
+        <v>0.6502287358547683</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.64008160099088</v>
+        <v>6.604013260161017</v>
       </c>
       <c r="D4" t="n">
-        <v>40.63355576597833</v>
+        <v>6.602952811971479</v>
       </c>
       <c r="E4" t="n">
-        <v>16.84883050814847</v>
+        <v>2.737934957574126</v>
       </c>
       <c r="F4" t="n">
-        <v>4.001407605260112</v>
+        <v>0.6502287358547683</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
